--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2020-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2020-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39B4C79E-8743-4727-94E6-89FFD7F65385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E46F727C-19E9-4DC2-A712-CC71CD983CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{6CEA9CF8-C8AC-4DA9-B209-7FE43DA181BF}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{79C53E2B-C2E0-4ADE-970C-A2ED8BCCCB53}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1571,25 +1571,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71619825-B37E-4B23-BBDC-52F4CC9D09C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3430FCF1-F276-43C3-8908-380B63AA8A1B}">
   <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1622,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1659,7 +1658,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1711,7 +1710,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1779,7 +1778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1851,7 +1850,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1923,7 +1922,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41"/>
       <c r="B7" s="42"/>
       <c r="C7" s="17" t="s">
@@ -1951,7 +1950,7 @@
       <c r="W7" s="48"/>
       <c r="X7" s="44"/>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2022</v>
       </c>
@@ -2023,7 +2022,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>2021</v>
       </c>
@@ -2095,7 +2094,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2020</v>
       </c>
@@ -2167,7 +2166,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2019</v>
       </c>
@@ -2239,7 +2238,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2018</v>
       </c>
@@ -2311,7 +2310,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>2017</v>
       </c>
@@ -2383,7 +2382,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2016</v>
       </c>
@@ -2455,7 +2454,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>2015</v>
       </c>
@@ -2527,7 +2526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2014</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2013</v>
       </c>
@@ -2671,7 +2670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2743,7 +2742,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="49">
         <v>2011</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="51">
         <v>2010</v>
       </c>
@@ -2887,7 +2886,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="53"/>
       <c r="B21" s="54"/>
       <c r="C21" s="20" t="s">
@@ -2915,7 +2914,7 @@
       <c r="W21" s="62"/>
       <c r="X21" s="56"/>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="49">
         <v>2009</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2008</v>
       </c>
@@ -3059,7 +3058,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="49">
         <v>2007</v>
       </c>
@@ -3131,7 +3130,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2006</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="49">
         <v>2005</v>
       </c>
@@ -3275,7 +3274,7 @@
         <v>7.72</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2004</v>
       </c>
@@ -3347,7 +3346,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="49">
         <v>2003</v>
       </c>
@@ -3419,7 +3418,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2002</v>
       </c>
@@ -3491,7 +3490,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="49">
         <v>2001</v>
       </c>
@@ -3563,7 +3562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2000</v>
       </c>
@@ -3635,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="49">
         <v>1999</v>
       </c>
@@ -3707,7 +3706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1998</v>
       </c>
@@ -3779,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="49">
         <v>1997</v>
       </c>
@@ -3851,7 +3850,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>1996</v>
       </c>
@@ -3923,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="49">
         <v>1995</v>
       </c>
@@ -3995,7 +3994,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1994</v>
       </c>
@@ -4067,7 +4066,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="49">
         <v>1993</v>
       </c>
@@ -4139,7 +4138,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1992</v>
       </c>
@@ -4211,7 +4210,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="49">
         <v>1991</v>
       </c>
@@ -4283,7 +4282,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1990</v>
       </c>
@@ -4355,7 +4354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="49">
         <v>1989</v>
       </c>
@@ -4427,7 +4426,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37" t="s">
         <v>57</v>
       </c>
